--- a/data/worldcup_0625_0623update.xlsx
+++ b/data/worldcup_0625_0623update.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -564,168 +564,172 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Who is the referee for France vs Iraq?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/who-is-the-referee-for-france-vs-iraq</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>France lived up to their pre-tournament billing when they dispatched Senegal 3-1 in their opening Group I clash last week.  The spotlight had firmly b</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2026-06-21T17:04:43</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
 The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2026-06-21T16:35:30</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
 The 2026 FIFA World Cup has completely ta</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-06-21T16:11:53</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
 The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Belgium vs Iran Prediction: World Cup 2026 Match Preview</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-06-21T03:52:12</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/belgium-vs-iran-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>After a balanced start left both of these sides with just one point each from their opening FIFA World Cup fixtures, we look ahead to Sunday’s clash w</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fastest World Cup to 100 goals in 68 years - are balls and breaks behind it?</t>
+          <t>Belgium vs Iran Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-20T23:46:26</t>
+          <t>2026-06-21T03:52:12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cvglnkw1l93o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://theanalyst.com/articles/belgium-vs-iran-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Messi, Mbappe and Vinicius Jr - the best World Cup goals from round one  The 2026 World Cup has become the fastest edition of the tournament to hit 10</t>
+          <t>After a balanced start left both of these sides with just one point each from their opening FIFA World Cup fixtures, we look ahead to Sunday’s clash w</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>扎卡：替补证明了瑞士的阵容深度；罚点前我跟曼赞比说你还年轻</t>
+          <t>Fastest World Cup to 100 goals in 68 years - are balls and breaks behind it?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-20 04:57</t>
+          <t>2026-06-20T23:46:26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5950591.html</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/cvglnkw1l93o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Messi, Mbappe and Vinicius Jr - the best World Cup goals from round one  The 2026 World Cup has become the fastest edition of the tournament to hit 10</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>创造历史，加拿大是首支世界杯单场进6球的中北美球队</t>
+          <t>扎卡：替补证明了瑞士的阵容深度；罚点前我跟曼赞比说你还年轻</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -735,12 +739,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-20 04:29</t>
+          <t>2026-06-20 04:57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5950533.html</t>
+          <t>https://www.dongqiudi.com/articles/5950591.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -748,112 +752,112 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>创造历史，加拿大是首支世界杯单场进6球的中北美球队</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-20 04:29</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5950533.html</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Was Canada’s Win Over Qatar the Most One-Sided Game in World Cup History?</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2026-06-19T15:12:21</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/canada-win-over-qatar-one-sided-world-cup-2026/</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>It was wave after wave after wave, only Qatar’s second match at the 2026 FIFA World Cup was anything but a day at the beach.
 World Cup co-hosts Canad</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>World Cup 2026: Routes to the final</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-06-19T12:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Canada 6-0 Qatar Stats: Hat-Trick Hero David Inspires Co-Hosts’ Historic First World Cup Win</t>
+          <t>World Cup 2026: Routes to the final</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>fifa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-19T00:20:51</t>
+          <t>2026-06-19T12:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/canada-vs-qatar-stats-world-cup-2026-live/</t>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Co-hosts Canada put on a show in front of their fans in Vancouver, firing six goals past a nine-man Qatar to secure a 6-0 win; the biggest FIFA World </t>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>盖村国家队战报：哲科卡蒂奇首发，十人波黑不敌瑞士</t>
+          <t>Canada 6-0 Qatar Stats: Hat-Trick Hero David Inspires Co-Hosts’ Historic First World Cup Win</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-19 15:05</t>
+          <t>2026-06-19T00:20:51</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5948740.html</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/canada-vs-qatar-stats-world-cup-2026-live/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Co-hosts Canada put on a show in front of their fans in Vancouver, firing six goals past a nine-man Qatar to secure a 6-0 win; the biggest FIFA World </t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>大卫完成帽子戏法，加拿大6球大胜首尝世界杯胜果</t>
+          <t>盖村国家队战报：哲科卡蒂奇首发，十人波黑不敌瑞士</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -863,12 +867,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-19 11:11</t>
+          <t>2026-06-19 15:05</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5948312.html</t>
+          <t>https://www.dongqiudi.com/articles/5948740.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -876,7 +880,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>世界杯B组前两轮积分榜：加拿大居首，下轮前二直接较量</t>
+          <t>大卫完成帽子戏法，加拿大6球大胜首尝世界杯胜果</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -886,12 +890,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-19 10:27</t>
+          <t>2026-06-19 11:11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5948244.html</t>
+          <t>https://www.dongqiudi.com/articles/5948312.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -899,112 +903,105 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Belgium vs Iran Bet Builder Tip: Consider Belgium to bounce back with 25/1 multi</t>
+          <t>世界杯B组前两轮积分榜：加拿大居首，下轮前二直接较量</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>squawka</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16 hours ago</t>
+          <t>2026-06-19 10:27</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.squawka.com/en/news/world-cup/belgium-vs-iran-bet-builder-21-06-26-world-cup/</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Belgium will be looking to respond after a frustrating opening draw against Egypt when they face Iran at the 2026 World Cup on Sunday night. Read on f</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5948244.html</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Belgium vs Iran Bet Builder Tip: Consider Belgium to bounce back with 25/1 multi</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16 hours ago</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/belgium-vs-iran-bet-builder-21-06-26-world-cup/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Belgium will be looking to respond after a frustrating opening draw against Egypt when they face Iran at the 2026 World Cup on Sunday night. Read on f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Miro Muheim Injury: Still training apart</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>rotowire</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>https://www.rotowire.com/soccer/headlines/miro-muheim-injury-still-training-apart-520472</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Written by RotoWire Staff
 Muheim (calf) continues to train separately from the Switzerland squad, spending the start of training sessions doing stren</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Shocking Sunderland stat re-emerges, following Brian Brobbey masterclass</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>fourfourtwo</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 20</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.fourfourtwo.com/competition/which-clubs-do-sunderland-have-more-players-than-at-the-2026-world-cup</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>In 2017/18, when Manchester City won the Premier League with 100 points, Sunderland were acclimating to Championship life.  The season prior, when Che</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Women’s T20 World Cup: West Indies defeat Sri Lanka by five wickets to stay unbeaten ahead of crunch England match</t>
+          <t>Miro Muheim Injury: Trains individually again Monday</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>skysports</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 14</t>
-        </is>
-      </c>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.skysports.com/cricket/news/12040/13556291/womens-t20-world-cup-west-indies-defeat-sri-lanka-by-five-wickets-to-stay-unbeaten-ahead-of-crunch-england-match</t>
+          <t>https://www.rotowire.com/soccer/headlines/miro-muheim-injury-trains-individually-again-monday-520557</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Captain Hayley Matthews and Stafanie Taylor lead the way for West Indies, who join England on six points atop Group B after five-wicket win in low-sco</t>
+          <t>Written by RotoWire Staff
+Muheim (calf) is only training individually and remains in question for Wednesday's match against Canada, according to Tobi</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>How far can the USA go at the 2026 World Cup? Hugely favourable route to semi-finals revealed</t>
+          <t>Shocking Sunderland stat re-emerges, following Brian Brobbey masterclass</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1014,179 +1011,233 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 08</t>
+          <t>Sat, 20 Jun 2026 20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.fourfourtwo.com/team/how-far-can-the-usa-go-at-the-2026-world-cup-hugely-favourable-route-to-semi-finals-revealed</t>
+          <t>https://www.fourfourtwo.com/competition/which-clubs-do-sunderland-have-more-players-than-at-the-2026-world-cup</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">As the group stage of the 2026 FIFA World Cup nears its conclusion, the United States Men’s National Team (USMNT) have positioned themselves strongly </t>
+          <t>In 2017/18, when Manchester City won the Premier League with 100 points, Sunderland were acclimating to Championship life.  The season prior, when Che</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>New Zealand World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
+          <t>Women’s T20 World Cup: West Indies defeat Sri Lanka by five wickets to stay unbeaten ahead of crunch England match</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>squawka</t>
+          <t>skysports</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7 hours ago</t>
+          <t>Sat, 20 Jun 2026 14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.squawka.com/en/news/world-cup/new-zealand-world-cup-2026-fixtures-squad-analysis/</t>
+          <t>https://www.skysports.com/cricket/news/12040/13556291/womens-t20-world-cup-west-indies-defeat-sri-lanka-by-five-wickets-to-stay-unbeaten-ahead-of-crunch-england-match</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>This summer marks New Zealand’s third appearance at a World Cup . They went unbeaten in their most recent appearance in 2010, but three draws wasn’t e</t>
+          <t>Captain Hayley Matthews and Stafanie Taylor lead the way for West Indies, who join England on six points atop Group B after five-wicket win in low-sco</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>How far can the USA go at the 2026 World Cup? Hugely favourable route to semi-finals revealed</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 08</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/team/how-far-can-the-usa-go-at-the-2026-world-cup-hugely-favourable-route-to-semi-finals-revealed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As the group stage of the 2026 FIFA World Cup nears its conclusion, the United States Men’s National Team (USMNT) have positioned themselves strongly </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>New Zealand World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>7 hours ago</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/new-zealand-world-cup-2026-fixtures-squad-analysis/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>This summer marks New Zealand’s third appearance at a World Cup . They went unbeaten in their most recent appearance in 2010, but three draws wasn’t e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Spain send statement with Saudi success</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2026-06-21T18:00:00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/spain-saudi-arabia-highlights-match-report</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>This is a modal window.
 Oyarzabal and Yamal on target in dominant display as Luis de la Fuente's side showed their class with a comprehensive Group H</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Brazil vs Haiti Prediction: World Cup 2026 Match Preview</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>theanalyst_api</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-06-19T21:55:38</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/brazil-vs-haiti-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Brazil are out to secure a first win of their World Cup 2026 campaign when they face off against Haiti in Philadelphia. Look ahead to the Group C cont</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Group B: What did we learn in the second round?</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sofascore</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-06-19T13:54:58</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://www.sofascore.com/news/group-b-what-did-we-learn-in-the-second-round</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Canada and Switzerland seized control of Group B with statement wins, while Bosnia and Qatar now face a decisive fight for survival.</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Brazil vs Haiti Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-06-19T21:55:38</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/brazil-vs-haiti-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Brazil are out to secure a first win of their World Cup 2026 campaign when they face off against Haiti in Philadelphia. Look ahead to the Group C cont</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Group B: What did we learn in the second round?</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-06-19T13:54:58</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/group-b-what-did-we-learn-in-the-second-round</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Canada and Switzerland seized control of Group B with statement wins, while Bosnia and Qatar now face a decisive fight for survival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Uruguay vs Cape Verde Bet Builder: Uruguay to dominate in our 13/1 tip for tonight</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>13 hours ago</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/uruguay-vs-cape-verde-bet-builder-21-06-2026/</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Uruguay will look to bring Cape Verde ‘s impressive unbeaten start to the 2026 World Cup to an end when the two nations meet in Group H at Hard Rock S</t>
         </is>
@@ -1802,7 +1853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1840,7 +1891,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Neymar completes first World Cup training session before Brazil vs. Scotland</t>
+          <t>Lawrence Shankland: Scotland not looking beyond crucial World Cup clash with Brazil</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1850,24 +1901,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-22T08:40:32</t>
+          <t>2026-06-22T20:10:53</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49142107/neymar-completes-first-world-cup-training-session-brazil-vs-scotland</t>
+          <t>https://www.espn.com/soccer/story/_/id/49146151/lawrence-shankland-scotland-focus-crucial-world-cup-clash-brazil</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neymar completed his first full training session with Brazil on Sunday.</t>
+          <t>Lawrence Shankland insists Scotland will ignore multiple permutations around possible qualification to go for the World Cup win against Brazil on Wedn</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lucas Paqueta: Brazil have 'great respect' for Scotland</t>
+          <t>Neymar completes first World Cup training session before Brazil vs. Scotland</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1877,47 +1928,51 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-21T23:39:02</t>
+          <t>2026-06-22T08:40:32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49138795/lucas-paqueta-brazil-scotland-fifa-world-cup-2026</t>
+          <t>https://www.espn.com/soccer/story/_/id/49142107/neymar-completes-first-world-cup-training-session-brazil-vs-scotland</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Brazil playmaker Lucas Paquetá says he has "great respect" for Scotland ahead of the decisive clash between the teams in Miami on Wednesday.</t>
+          <t>Neymar completed his first full training session with Brazil on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>官方：墨西哥裁判拉莫斯将执法世界杯苏格兰vs巴西</t>
+          <t>Lucas Paqueta: Brazil have 'great respect' for Scotland</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-21 20:39</t>
+          <t>2026-06-21T23:39:02</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955264.html</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>https://www.espn.com/soccer/story/_/id/49138795/lucas-paqueta-brazil-scotland-fifa-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Brazil playmaker Lucas Paquetá says he has "great respect" for Scotland ahead of the decisive clash between the teams in Miami on Wednesday.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>苏格兰主帅：对摩洛哥我们踢得有点慢热；末轮要死磕巴西</t>
+          <t>官方：墨西哥裁判拉莫斯将执法世界杯苏格兰vs巴西</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1927,12 +1982,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-21 00:26</t>
+          <t>2026-06-21 20:39</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953238.html</t>
+          <t>https://www.dongqiudi.com/articles/5955264.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1940,34 +1995,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+          <t>苏格兰主帅：对摩洛哥我们踢得有点慢热；末轮要死磕巴西</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 13</t>
+          <t>2026-06-21 00:26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953238.html</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1977,24 +2028,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 09</t>
+          <t>Sun, 21 Jun 2026 13</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
+          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2004,24 +2055,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 04</t>
+          <t>Sun, 21 Jun 2026 09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
+          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2031,24 +2082,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sun Jun 21 2026 15:</t>
+          <t>Sun, 21 Jun 2026 04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saibari strikes after 70 seconds as Morocco puncture Scotland’s World Cup party</t>
+          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2058,24 +2109,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sat, 20 Jun 2026 00</t>
+          <t>Sun Jun 21 2026 15:</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/20/scotland-morocco-world-cup-match-report</t>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scotland would have taken this outcome after 70 seconds. Ismael Saibiri had fired this highly rated Morocco team ahead. Men in kilts gulped under the </t>
+          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
+          <t>Saibari strikes after 70 seconds as Morocco puncture Scotland’s World Cup party</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2085,96 +2136,150 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fri, 19 Jun 2026 10</t>
+          <t>Sat, 20 Jun 2026 00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
+          <t>https://www.theguardian.com/football/2026/jun/20/scotland-morocco-world-cup-match-report</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
+          <t xml:space="preserve">Scotland would have taken this outcome after 70 seconds. Ismael Saibiri had fired this highly rated Morocco team ahead. Men in kilts gulped under the </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Name the seven Scotland survivors from Clarke's first squad</t>
+          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-22T07:46:18</t>
+          <t>Fri, 19 Jun 2026 10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c05yze49v71o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Seven years have passed since Steve Clarke named his first Scotland squad for Euro 2020 qualifiers against Cyprus and Belgium.  Seven players from tha</t>
+          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Scotland's 2026 World Cup squad: All 26 players picked by Steve Clarke and why</t>
+          <t>How Ferguson became Scotland's most influential World Cup player</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-22T06:34:52</t>
+          <t>2026-06-22T17:39:02</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/48769157/meet-scotland-2026-world-cup-squad-all-26-players-picked-steve-clarke-why</t>
+          <t>https://www.bbc.com/sport/football/articles/c20y1zj927jo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Scotland manager Steve Clarke has named the 26 players he believes can make an impression at the 2026 World Cup in the United States, Canada and Mexic</t>
+          <t>Lewis Ferguson earned his 26th Scotland cap in the 1-0 defeat to Morocco  Eight years ago, Lewis Ferguson had just departed Hamilton Academical.  A mu</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Name the seven Scotland survivors from Clarke's first squad</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-22T07:46:18</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c05yze49v71o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Seven years have passed since Steve Clarke named his first Scotland squad for Euro 2020 qualifiers against Cyprus and Belgium.  Seven players from tha</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Scotland's 2026 World Cup squad: All 26 players picked by Steve Clarke and why</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-22T06:34:52</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/48769157/meet-scotland-2026-world-cup-squad-all-26-players-picked-steve-clarke-why</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Scotland manager Steve Clarke has named the 26 players he believes can make an impression at the 2026 World Cup in the United States, Canada and Mexic</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>4-0突尼斯，日本终结连续5届世界杯小组赛第二轮不胜魔咒</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>2026-06-22 07:41</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956343</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>世界杯小组赛第二轮，日本对阵突尼斯，最终日本国家队4-0大胜突尼斯。
 据统计，日本本轮大胜后终结了连续5届世界杯小组赛第二轮不胜魔咒，自2006年世界杯以来，日本队在世界杯小组赛第二轮未尝胜绩，本届世界杯终于打破魔咒。
@@ -2184,64 +2289,10 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Does it matter if Scotland lose and still make history?</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-06-21T21:39:43</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Scotland World Cup injury concerns as Aaron Hickey, Scott McKenna, Lewis Ferguson miss training</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>espn_pw</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-06-21T21:00:44</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://www.espn.com/soccer/story/_/id/49135824/scotland-injury-concerns-aaron-hickey-scott-mckenna-lewis-ferguson-miss-training-world-cup</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Aaron Hickey, Scott McKenna and Lewis Ferguson missed group training ahead of Scotland's final World Cup Group C fixture against Brazil on Wednesday.</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>What have we learned from Scotland's World Cup so far?</t>
+          <t>Does it matter if Scotland lose and still make history?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2251,70 +2302,78 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-21T13:14:21</t>
+          <t>2026-06-21T21:39:43</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c79yq0yx10ro?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Steve Clarke is bidding to become the first manager to steer Scotland beyond the group stage of a major tournament  After two World Cup outings, Scotl</t>
+          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>官方：巴西裁判阿巴蒂将执法世界杯瑞士vs加拿大</t>
+          <t>Scotland World Cup injury concerns as Aaron Hickey, Scott McKenna, Lewis Ferguson miss training</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-21 20:48</t>
+          <t>2026-06-21T21:00:44</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955280.html</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>https://www.espn.com/soccer/story/_/id/49135824/scotland-injury-concerns-aaron-hickey-scott-mckenna-lewis-ferguson-miss-training-world-cup</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aaron Hickey, Scott McKenna and Lewis Ferguson missed group training ahead of Scotland's final World Cup Group C fixture against Brazil on Wednesday.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>荷兰5球大胜瑞典，世界杯连续不败场次超越贝利时代巴西</t>
+          <t>What have we learned from Scotland's World Cup so far?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-21 20:21</t>
+          <t>2026-06-21T13:14:21</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955233.html</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/c79yq0yx10ro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Steve Clarke is bidding to become the first manager to steer Scotland beyond the group stage of a major tournament  After two World Cup outings, Scotl</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>巴媒：内马尔恢复有球训练，力争对苏格兰完成世界杯首秀</t>
+          <t>官方：巴西裁判阿巴蒂将执法世界杯瑞士vs加拿大</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2324,12 +2383,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-21 07:27</t>
+          <t>2026-06-21 20:48</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953848.html</t>
+          <t>https://www.dongqiudi.com/articles/5955280.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -2337,218 +2396,218 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Neymar set for Scotland return as Raphinha faces World Cup setback</t>
+          <t>荷兰5球大胜瑞典，世界杯连续不败场次超越贝利时代巴西</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-20T16:28:34</t>
+          <t>2026-06-21 20:21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/neymar-set-for-scotland-return-as-raphinha-faces-world-cup-setback</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carlo Ancelotti has confirmed he expects Neymar to be available for Brazil’s final Group C match against Scotland at the World Cup. However, Raphinha </t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955233.html</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>How does qualification for the World Cup knockout stage work?</t>
+          <t>巴媒：内马尔恢复有球训练，力争对苏格兰完成世界杯首秀</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-20T16:24:00</t>
+          <t>2026-06-21 07:27</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953848.html</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Neymar set for Scotland return as Raphinha faces World Cup setback</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:28:34</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/neymar-set-for-scotland-return-as-raphinha-faces-world-cup-setback</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carlo Ancelotti has confirmed he expects Neymar to be available for Brazil’s final Group C match against Scotland at the World Cup. However, Raphinha </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>How does qualification for the World Cup knockout stage work?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:24:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Cunha riding wave of success after brilliant Brazil brace</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>2026-06-20T05:40:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/matheus-cunha-brazil-reaction-haiti</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Four years after missing out on Qatar 2022, surfing fan Matheus Cunha scored his first FIFA World Cup goals as Brazil beat Haiti 3-0.
 After waiting f</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>The best photos from Matchday 9</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>2026-06-20T05:00:00</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/best-photos-matchday-9</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Enjoy an array of the best photos from the most recent round of fixtures at the FIFA World Cup 2026.
 Two USA fans dressed as bald eagles pose ahead o</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Six players climbing the FIFA Power Rankings</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>2026-06-20T04:00:00</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/six-players-climbing-fifa-power-rankings</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">From Jonathan David and Matheus Cunha to Lucas Paqueta and Chris Richards, see which players have risen swiftly up the FIFA Power Rankings.
 Jonathan </t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Vinicius Jr. hits the ground running with Brazil</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-06-20T04:00:00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/vinicius-jr-brazil-great-start</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>The No. 7 has been involved in all of Brazil's goals so far in the World Cup and has surpassed stars like Romario and Ronaldinho in efficiency per gam</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>巴西队美加墨周期纪实39：世界杯小组赛3-0轻取海地</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-06-20 17:59</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5951203.html</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-    </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>老熟人来了，瓜迪奥拉现身世界杯球场看台观战苏格兰vs摩洛哥</t>
+          <t>Vinicius Jr. hits the ground running with Brazil</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>fifa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-20 14:52</t>
+          <t>2026-06-20T04:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951666.html</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>https://www.fifa.com/en/articles/vinicius-jr-brazil-great-start</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>The No. 7 has been involved in all of Brazil's goals so far in the World Cup and has surpassed stars like Romario and Ronaldinho in efficiency per gam</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>巴西3-0海地登顶C组，卡塞米罗：世界杯无易战</t>
+          <t>巴西队美加墨周期纪实39：世界杯小组赛3-0轻取海地</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2558,12 +2617,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-20 12:56</t>
+          <t>2026-06-20 17:59</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951477.html</t>
+          <t>https://www.dongqiudi.com/articles/5951203.html</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -2571,7 +2630,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>世界杯积分新规，巴西3:0海地，海地成为第一支出...</t>
+          <t>老熟人来了，瓜迪奥拉现身世界杯球场看台观战苏格兰vs摩洛哥</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2581,12 +2640,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-20 10:46</t>
+          <t>2026-06-20 14:52</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951242.html</t>
+          <t>https://www.dongqiudi.com/articles/5951666.html</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -2594,7 +2653,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8胜1平8次零封，巴西在世界杯面对中北美球队战绩碾压</t>
+          <t>巴西3-0海地登顶C组，卡塞米罗：世界杯无易战</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2604,12 +2663,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-20 07:12</t>
+          <t>2026-06-20 12:56</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5950880.html</t>
+          <t>https://www.dongqiudi.com/articles/5951477.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -2617,88 +2676,80 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazil vs Haiti Prediction: World Cup 2026 Match Preview</t>
+          <t>世界杯积分新规，巴西3:0海地，海地成为第一支出...</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-06-19T21:55:38</t>
+          <t>2026-06-20 10:46</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/brazil-vs-haiti-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Brazil are out to secure a first win of their World Cup 2026 campaign when they face off against Haiti in Philadelphia. Look ahead to the Group C cont</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5951242.html</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazil vs Haiti preview: Group C stakes, key trends and a few numbers you’ll want to know</t>
+          <t>8胜1平8次零封，巴西在世界杯面对中北美球队战绩碾压</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06-19T13:00:00</t>
+          <t>2026-06-20 07:12</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/brazil-vs-haiti-preview-group-c-stakes-key-trends-and-a-few-numbers-youll-want-to-know</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Brazil face Haiti in World Cup 2026 Group C. Form trends, key stats, decimal odds, team news and Sofascore Rating standouts to know before kickoff.</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5950880.html</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>World Cup 2026: Routes to the final</t>
+          <t>Brazil vs Haiti Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-06-19T12:00:00</t>
+          <t>2026-06-19T21:55:38</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
+          <t>https://theanalyst.com/articles/brazil-vs-haiti-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
+          <t>Brazil are out to secure a first win of their World Cup 2026 campaign when they face off against Haiti in Philadelphia. Look ahead to the Group C cont</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Scotland vs Morocco preview: World Cup Group C</t>
+          <t>Brazil vs Haiti preview: Group C stakes, key trends and a few numbers you’ll want to know</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2708,162 +2759,171 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-06-19T12:00:00</t>
+          <t>2026-06-19T13:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/scotland-vs-morocco-preview-world-cup-group-c</t>
+          <t>https://www.sofascore.com/news/brazil-vs-haiti-preview-group-c-stakes-key-trends-and-a-few-numbers-youll-want-to-know</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Scotland face Morocco at Gillette Stadium in World Cup 2026 Group C. Form, H2H, odds, lineups and the key Sofascore Rating standouts set the stage.</t>
+          <t>Brazil face Haiti in World Cup 2026 Group C. Form trends, key stats, decimal odds, team news and Sofascore Rating standouts to know before kickoff.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Scotland vs Morocco Prediction: World Cup 2026 Match Preview</t>
+          <t>World Cup 2026: Routes to the final</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>fifa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-06-19T08:13:48</t>
+          <t>2026-06-19T12:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/scotland-vs-morocco-prediction-world-cup-2026-match-preview/</t>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>After a pair of exciting curtain-raisers, the top two sides in Group C will now face off in Boston. Look ahead to Friday’s FIFA World Cup clash with o</t>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>How sweltering Scotland can handle World Cup heat</t>
+          <t>Scotland vs Morocco preview: World Cup Group C</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-06-17T11:16:20</t>
+          <t>2026-06-19T12:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.sofascore.com/news/scotland-vs-morocco-preview-world-cup-group-c</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
+          <t>Scotland face Morocco at Gillette Stadium in World Cup 2026 Group C. Form, H2H, odds, lineups and the key Sofascore Rating standouts set the stage.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>联手梅西！罗马诺：卡塞米罗还收到欧洲沙特报价 他与迈阿密签3年</t>
+          <t>Scotland vs Morocco Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>zhibo8</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-06-22 15:35:00</t>
+          <t>2026-06-19T08:13:48</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e37c69ad1native.htm</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/scotland-vs-morocco-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>After a pair of exciting curtain-raisers, the top two sides in Group C will now face off in Boston. Look ahead to Friday’s FIFA World Cup clash with o</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>帕奎塔：和维尼修斯一起踢球很快乐；我们都为内马尔回归高兴</t>
+          <t>How sweltering Scotland can handle World Cup heat</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-06-22 03:33</t>
+          <t>2026-06-17T11:16:20</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955960.html</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ESPN：内马尔将入选对阵苏格兰比赛名单，但不会扮演重要角色</t>
+          <t>Neymar Injury: Trains without limitations</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:48</t>
-        </is>
-      </c>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955754.html</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>https://www.rotowire.com/soccer/headlines/neymar-injury-trains-without-limitations-520556</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Neymar (calf) trained without limitations Monday as his availability for Wednesday's match against Scotland is further rein</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TA：巴西全民紧盯内马尔和恩德里克，真正的救星却是库尼亚</t>
+          <t>联手梅西！罗马诺：卡塞米罗还收到欧洲沙特报价 他与迈阿密签3年</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>zhibo8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-06-22 00:02</t>
+          <t>2026-06-22 15:35:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955612.html</t>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e37c69ad1native.htm</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2871,7 +2931,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>利物浦球员国家队战报：阿利松80场里程碑多次扑救+零封</t>
+          <t>帕奎塔：和维尼修斯一起踢球很快乐；我们都为内马尔回归高兴</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2881,12 +2941,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-06-20 11:15</t>
+          <t>2026-06-22 03:33</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951315.html</t>
+          <t>https://www.dongqiudi.com/articles/5955960.html</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2894,181 +2954,269 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maybe this World Cup will bring the best out of the US, not the worst</t>
+          <t>ESPN：内马尔将入选对阵苏格兰比赛名单，但不会扮演重要角色</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 04</t>
+          <t>2026-06-22 00:48</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-2026-us-united-states-usa-co-host-nation</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Tournament could hold up a useful hand mirror to the isolationism and divisiveness of Trump’s joint-host nation  O ne of the best parts of following f</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955754.html</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>TA：巴西全民紧盯内马尔和恩德里克，真正的救星却是库尼亚</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:02</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955612.html</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>利物浦球员国家队战报：阿利松80场里程碑多次扑救+零封</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-06-20 11:15</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5951315.html</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>图片报：检察机关调查博彩运营商Blaze，内马尔曾与之合作</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959123&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Maybe this World Cup will bring the best out of the US, not the worst</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 04</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-2026-us-united-states-usa-co-host-nation</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Tournament could hold up a useful hand mirror to the isolationism and divisiveness of Trump’s joint-host nation  O ne of the best parts of following f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>What did we learn after the second round of Group C</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>sofascore</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>2026-06-21T15:21:15</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>https://www.sofascore.com/news/what-did-we-learn-after-the-second-round-of-group-c</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Aimar: Messi has made us expect the unexpected</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>2026-06-21T03:30:00</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/pablo-aimar-messi</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Lionel Scaloni’s assistant on the Argentina bench discusses his relationship with the captain and La Albiceleste’s recent success.
 At the age of 12 o</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Scotland 0-1 Morocco Stats: Early Saibari Stunner Settles Group C Clash</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>theanalyst</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>2026-06-20T01:12:39</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/scotland-vs-morocco-stats-fifa-world-cup-2026-live</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Follow the action live as Scotland look to make it two wins from two at the 2026 FIFA World Cup against African giants Morocco.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>C组积分榜：巴西积4分领先摩洛哥2粒净胜球，海地提前出局</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>dongqiudi_team</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>2026-06-20 10:44</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/articles/5951239.html</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Spain World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>15 hours ago</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/spain-world-cup-2026-fixtures-results-squad-analysis/</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Spain ’s 2026 World Cup campaign took a sharp turn in North America as they followed up a frustrating opening draw with Cape Verde by producing a comm</t>
         </is>
@@ -3085,7 +3233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -3900,130 +4048,157 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>What did we learn after the second round of Group C</t>
+          <t>How Ferguson became Scotland's most influential World Cup player</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06-21T15:21:15</t>
+          <t>2026-06-22T17:39:02</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/what-did-we-learn-after-the-second-round-of-group-c</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/c20y1zj927jo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Lewis Ferguson earned his 26th Scotland cap in the 1-0 defeat to Morocco  Eight years ago, Lewis Ferguson had just departed Hamilton Academical.  A mu</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>What did we learn after the second round of Group C</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-21T15:21:15</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/what-did-we-learn-after-the-second-round-of-group-c</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Aimar: Messi has made us expect the unexpected</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>2026-06-21T03:30:00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/pablo-aimar-messi</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Lionel Scaloni’s assistant on the Argentina bench discusses his relationship with the captain and La Albiceleste’s recent success.
 At the age of 12 o</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>How does qualification for the World Cup knockout stage work?</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>2026-06-20T16:24:00</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Scotland 0-1 Morocco Stats: Early Saibari Stunner Settles Group C Clash</t>
+          <t>How does qualification for the World Cup knockout stage work?</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>theanalyst</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-06-20T01:12:39</t>
+          <t>2026-06-20T16:24:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/scotland-vs-morocco-stats-fifa-world-cup-2026-live</t>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Follow the action live as Scotland look to make it two wins from two at the 2026 FIFA World Cup against African giants Morocco.</t>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Scotland 0-1 Morocco Stats: Early Saibari Stunner Settles Group C Clash</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-06-20T01:12:39</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/scotland-vs-morocco-stats-fifa-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Follow the action live as Scotland look to make it two wins from two at the 2026 FIFA World Cup against African giants Morocco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Spain World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>15 hours ago</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/spain-world-cup-2026-fixtures-results-squad-analysis/</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Spain ’s 2026 World Cup campaign took a sharp turn in North America as they followed up a frustrating opening draw with Cape Verde by producing a comm</t>
         </is>
@@ -4040,7 +4215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4155,160 +4330,164 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>墨西哥前区长世界杯热舞，大方回应着装争议</t>
+          <t>Merlin the viral World Cup duck got to meet the Mexican President</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-22 11:19</t>
+          <t>2026-06-22T17:45:44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956722.html</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>https://www.espn.com/video/clip/_/id/49145310/merlin-viral-world-cup-duck-got-meet-mexican-president</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Merlin the viral World Cup duck got to meet the Mexican President</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>墨西哥前区长世界杯热舞，大方回应着装争议</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:19</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956722.html</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>World Cup on Fubo: Free trials, deals, offers, subscriptions, plans and more</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2026-06-21T18:22:43</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-fubo/blt5f97df30090df47f</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">GOAL explains how fans can stream live 2026 FIFA World Cup matches with Fubo
 The 2026 FIFA World Cup is officially underway, treating soccer fans to </t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>官方：墨西哥裁判拉莫斯将执法世界杯苏格兰vs巴西</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-06-21 20:39</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955264.html</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>官方：墨西哥裁判拉莫斯将执法世界杯苏格兰vs巴西</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-21 20:39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5955264.html</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Most FIFA World Cup Appearances by a Player</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-06-20T19:39:34</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/most-world-cup-appearances-by-a-player/</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Here are the players who have combined longevity and excellence to record the most men’s FIFA World Cup appearances of all time.
 Lionel Messi: Argent</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Most Red Cards in World Cup History: Players, Teams and Incidents That Made History</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2026-06-20T19:21:25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/most-red-cards-in-world-cup-history/</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">From Zinedine Zidane’s headbutt to Wayne Rooney’s stamp, discover which players and teams have received the most red cards in FIFA World Cup history.
 </t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FIFA拒绝向奥乔亚授予世界杯传奇徽章，墨西哥足协考虑上诉</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-06-20 06:10</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5950731.html</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>遇到克星，亚洲球队世界杯对墨西哥6战全败</t>
+          <t>FIFA拒绝向奥乔亚授予世界杯传奇徽章，墨西哥足协考虑上诉</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4318,12 +4497,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-20 00:21</t>
+          <t>2026-06-20 06:10</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5950184.html</t>
+          <t>https://www.dongqiudi.com/articles/5950731.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -4331,344 +4510,421 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>World Cup 2026: Routes to the final</t>
+          <t>遇到克星，亚洲球队世界杯对墨西哥6战全败</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-19T12:00:00</t>
+          <t>2026-06-20 00:21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5950184.html</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mexico Extend Incredible 100% World Cup Record Against South Korea</t>
+          <t>World Cup 2026: Routes to the final</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>fifa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-19T07:58:38</t>
+          <t>2026-06-19T12:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/mexico-extend-incredible-100-world-cup-record-against-south-korea</t>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mexico beat South Korea in 1998, 2018 and 2026 at the FIFA World Cup. Key stats, shot maps and Sofascore Ratings explain how each game tilted Mexico’s</t>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FIFA World Cup Hat-Tricks: The Facts</t>
+          <t>Mexico Extend Incredible 100% World Cup Record Against South Korea</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-19T00:28:32</t>
+          <t>2026-06-19T07:58:38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/world-cup-hat-tricks-fifa/</t>
+          <t>https://www.sofascore.com/news/mexico-extend-incredible-100-world-cup-record-against-south-korea</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>There have been 56 hat-tricks scored in men’s FIFA World Cup finals tournaments. We give a rundown of the best facts about World Cup hat-tricks, as we</t>
+          <t>Mexico beat South Korea in 1998, 2018 and 2026 at the FIFA World Cup. Key stats, shot maps and Sofascore Ratings explain how each game tilted Mexico’s</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>世界杯A组前两轮积分榜：墨西哥居首，韩国第二</t>
+          <t>FIFA World Cup Hat-Tricks: The Facts</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-19 11:00</t>
+          <t>2026-06-19T00:28:32</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5948291.html</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>https://theanalyst.com/articles/world-cup-hat-tricks-fifa/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>There have been 56 hat-tricks scored in men’s FIFA World Cup finals tournaments. We give a rundown of the best facts about World Cup hat-tricks, as we</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>世界杯A组前两轮积分榜：墨西哥居首，韩国第二</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-19 11:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5948291.html</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>David Jurasek Injury: World Cup likely over</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>rotowire</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>https://www.rotowire.com/soccer/headlines/david-jurasek-injury-world-cup-likely-over-520470</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">Written by RotoWire Staff
 Jurasek is likely out for the remainder of the World Cup after suffering a muscle injury in the pre-match training session </t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Bracketology: predict a path to World Cup victory</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>guardian</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Thu, 04 Jun 2026 10</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Australia’s Jackson Irvine has no sympathy for Paraguay after historic World Cup red card</t>
+          <t>Has a World Cup game ever been abandoned before?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>fourfourtwo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 04</t>
+          <t>Tue, 23 Jun 2026 00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/australias-jackson-irvine-has-no-sympathy-for-paraguay-after-historic-world-cup-red-card</t>
+          <t>https://www.fourfourtwo.com/competition/has-a-world-cup-game-ever-been-abandoned-before</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Miguel Almirón sent off against Turkey for covering mouth  Socceroos face South Americans in crucial last Group D match  Socceroo Jackson Irvine has b</t>
+          <t>France vs Iraq at the 2026 World Cup kicked off at 9pm British time this evening, with Kylian Mbappe scoring the first half's only goal.  The Real Mad</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Bracketology: predict a path to World Cup victory</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Australia’s Jackson Irvine has no sympathy for Paraguay after historic World Cup red card</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 04</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/australias-jackson-irvine-has-no-sympathy-for-paraguay-after-historic-world-cup-red-card</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Miguel Almirón sent off against Turkey for covering mouth  Socceroos face South Americans in crucial last Group D match  Socceroo Jackson Irvine has b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Semenyo and Ghana out to emulate 2010 World Cup heroes as they face England</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 18</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/antoine-semenyo-ghana-2010-world-cup-team-england</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Carlos Queiroz’s squad hope to repeat the form that almost made Ghana the first African team to reach the semi-finals  A ntoine Semenyo was only 10 ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Egypt World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>7 hours ago</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/egypt-world-cup-2026-fixtures-players-analysis/</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Egypt are at the World Cup for the fourth time in their history. And they’ll be hoping to make it past the group stage for the first time.
 After a 1-</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Does it matter if Scotland lose and still make history?</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026-06-21T21:39:43</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>How sweltering Scotland can handle World Cup heat</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2026-06-17T11:16:20</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Belgium World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>squawka</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>12 hours ago</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://www.squawka.com/en/news/world-cup/belgium-world-cup-2026-fixtures-squad-analysis-june-21/</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Belgium are back at the World Cup and desperate to give a much-improved account of themselves on the biggest stage. The Red Devils have got off to a s</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Does it matter if Scotland lose and still make history?</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-21T21:39:43</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>How sweltering Scotland can handle World Cup heat</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-17T11:16:20</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Belgium World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>12 hours ago</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/belgium-world-cup-2026-fixtures-squad-analysis-june-21/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Belgium are back at the World Cup and desperate to give a much-improved account of themselves on the biggest stage. The Red Devils have got off to a s</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Argentina vs Austria: predictions, best bets, stats &amp; odds</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>1 hour ago</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/argentina-vs-austria-predictions-betting-tips-22-06-26/</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">No previous meetings between these teams.
 No price boosts for this event.
@@ -4678,31 +4934,55 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>World Cup 2026 Group F: Latest table, fixtures and results</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>1 day ago</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-group-f-latest-table-fixtures-and-results/</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t xml:space="preserve">Group F at World Cup 2026 looks to be one that has the potential for the biggest shock.
 The draw placed Netherlands into Group F alongside Japan and </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cristian Romero Injury: Set for testing, hopeful of minor injury</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/cristian-romero-injury-set-for-testing-hopeful-of-minor-injury-520551</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Romero (knee) is set for testing in the coming days, but is not expected to be anything significant, according to manager L</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -4755,30 +5035,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>官方：阿根廷裁判特略将执法世界杯南非vs韩国</t>
+          <t>South Africa vs. South Korea  at World Cup 2026: TV channel, how to watch, kick-off time, live stream, referee, predicted line-ups</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-21 20:43</t>
+          <t>2026-06-22T17:24:30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955267.html</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>https://www.espn.com/soccer/story/_/id/49144478/fifa-world-cup-2026-south-africa-vs-south-korea-channel-how-watch-kickoff-live-stream-referee-predicted-line-ups</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Everything you need to know ahead of the World Cup Group A finale between South Africa and South Korea.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>黄仁范：韩国0-1墨西哥但不会低落，战南非相信能赢</t>
+          <t>官方：阿根廷裁判特略将执法世界杯南非vs韩国</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4788,12 +5072,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-19 13:04</t>
+          <t>2026-06-21 20:43</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5948486.html</t>
+          <t>https://www.dongqiudi.com/articles/5955267.html</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -4801,7 +5085,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>韩国前国脚李荣杓：日本队世界杯夺冠大概在1%左右</t>
+          <t>黄仁范：韩国0-1墨西哥但不会低落，战南非相信能赢</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4811,12 +5095,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-22 11:07</t>
+          <t>2026-06-19 13:04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5956690.html</t>
+          <t>https://www.dongqiudi.com/articles/5948486.html</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -4824,25 +5108,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Semenyo and Ghana out to emulate 2010 World Cup heroes as they face England</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 18</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/antoine-semenyo-ghana-2010-world-cup-team-england</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Carlos Queiroz’s squad hope to repeat the form that almost made Ghana the first African team to reach the semi-finals  A ntoine Semenyo was only 10 ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>韩国前国脚李荣杓：日本队世界杯夺冠大概在1%左右</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-22 11:07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5956690.html</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>4-0突尼斯，日本终结连续5届世界杯小组赛第二轮不胜魔咒</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2026-06-22 07:41</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956343</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>世界杯小组赛第二轮，日本对阵突尼斯，最终日本国家队4-0大胜突尼斯。
 据统计，日本本轮大胜后终结了连续5届世界杯小组赛第二轮不胜魔咒，自2006年世界杯以来，日本队在世界杯小组赛第二轮未尝胜绩，本届世界杯终于打破魔咒。
@@ -4852,588 +5186,615 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>World Cup on Fubo: Free trials, deals, offers, subscriptions, plans and more</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2026-06-21T18:22:43</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-fubo/blt5f97df30090df47f</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">GOAL explains how fans can stream live 2026 FIFA World Cup matches with Fubo
 The 2026 FIFA World Cup is officially underway, treating soccer fans to </t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Pacific Time (PT) Schedule</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2026-06-21T17:04:43</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-pacific-time-schedule/blt708391eb6f8f1517</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Pacific Time Zone
 The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Mountain Time (MT) Schedule</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2026-06-21T16:35:30</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-mountain-time-schedule/blt2141270bc47c494f</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Mountain Time Zone
 The 2026 FIFA World Cup has completely ta</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Today's World Cup 2026 Kickoff Times: Complete Eastern Time (ET) Schedule</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>goal_pw</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2026-06-21T16:11:53</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.goal.com/en/news/world-cup-2026-eastern-time/blt57a4c6b10cc97d94</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>An all-you-need-to-know guide on how to watch every World Cup game broadcast live in the Eastern Time Zone
 The 2026 FIFA World Cup has completely tak</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Fastest World Cup to 100 goals in 68 years - are balls and breaks behind it?</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>bbc_sport</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2026-06-20T23:46:26</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.bbc.com/sport/football/articles/cvglnkw1l93o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Messi, Mbappe and Vinicius Jr - the best World Cup goals from round one  The 2026 World Cup has become the fastest edition of the tournament to hit 10</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Most FIFA World Cup Appearances by a Player</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>2026-06-20T19:39:34</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/most-world-cup-appearances-by-a-player/</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Here are the players who have combined longevity and excellence to record the most men’s FIFA World Cup appearances of all time.
 Lionel Messi: Argent</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Most Red Cards in World Cup History: Players, Teams and Incidents That Made History</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>theanalyst_api</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>2026-06-20T19:21:25</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://theanalyst.com/articles/most-red-cards-in-world-cup-history/</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">From Zinedine Zidane’s headbutt to Wayne Rooney’s stamp, discover which players and teams have received the most red cards in FIFA World Cup history.
 </t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>韩足晚报（26.6.20）韩国便利店借世界杯营销，获成功</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-06-20 21:11</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5951847.html</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>World Cup 2026: Routes to the final</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-06-19T12:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
-        </is>
-      </c>
-    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mexico Extend Incredible 100% World Cup Record Against South Korea</t>
+          <t>韩足晚报（26.6.20）韩国便利店借世界杯营销，获成功</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-19T07:58:38</t>
+          <t>2026-06-20 21:11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/mexico-extend-incredible-100-world-cup-record-against-south-korea</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Mexico beat South Korea in 1998, 2018 and 2026 at the FIFA World Cup. Key stats, shot maps and Sofascore Ratings explain how each game tilted Mexico’s</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5951847.html</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>世界杯A组前两轮积分榜：墨西哥居首，韩国第二</t>
+          <t>World Cup 2026: Routes to the final</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>fifa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-19 11:00</t>
+          <t>2026-06-19T12:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5948291.html</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Mexico Extend Incredible 100% World Cup Record Against South Korea</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-19T07:58:38</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/mexico-extend-incredible-100-world-cup-record-against-south-korea</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Mexico beat South Korea in 1998, 2018 and 2026 at the FIFA World Cup. Key stats, shot maps and Sofascore Ratings explain how each game tilted Mexico’s</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>世界杯A组前两轮积分榜：墨西哥居首，韩国第二</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-19 11:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5948291.html</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>武磊：感觉日本队每一个位置都没有短板，整体非常强大</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>2026-06-22 08:32</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956412</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>2026美加墨世界杯小组赛第2轮角逐，日本队4-0大胜突尼斯队。上海海港球员武磊在连线节目中表示：“感觉日本队每一个位置都没有短板，整体非常强大。”
 武磊说道：“我觉得现在日本队整体非常强大，每一个位置感觉都比较平均，好像没有哪一个位置稍弱一点。就像刚才说的，前锋位置上，不只是一个得分点，有很多得分</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>奇诚庸：孙兴慜的速度仍然很快，他在边路更有威胁</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-06-21 08:58</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5954002.html</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>奥贝德：韩国不仅有孙兴慜，李刚仁也是一位非常出色的球员</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-06-20 07:53</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5950944.html</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bracketology: predict a path to World Cup victory</t>
+          <t>奇诚庸：孙兴慜的速度仍然很快，他在边路更有威胁</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thu, 04 Jun 2026 10</t>
+          <t>2026-06-21 08:58</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5954002.html</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Australia’s Jackson Irvine has no sympathy for Paraguay after historic World Cup red card</t>
+          <t>奥贝德：韩国不仅有孙兴慜，李刚仁也是一位非常出色的球员</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 04</t>
+          <t>2026-06-20 07:53</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/australias-jackson-irvine-has-no-sympathy-for-paraguay-after-historic-world-cup-red-card</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Miguel Almirón sent off against Turkey for covering mouth  Socceroos face South Americans in crucial last Group D match  Socceroo Jackson Irvine has b</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5950944.html</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Has a World Cup game ever been abandoned before?</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fourfourtwo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.fourfourtwo.com/competition/has-a-world-cup-game-ever-been-abandoned-before</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>France vs Iraq at the 2026 World Cup kicked off at 9pm British time this evening, with Kylian Mbappe scoring the first half's only goal.  The Real Mad</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bracketology: predict a path to World Cup victory</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Thu, 04 Jun 2026 10</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/ng-interactive/2026/jun/04/bracketology-predict-a-path-to-world-cup-victory</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Click your way through the group stage and the knockouts to crown champion  Groups Touch and drag teams into predicted finish order  Third-place teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Australia’s Jackson Irvine has no sympathy for Paraguay after historic World Cup red card</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 04</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/21/australias-jackson-irvine-has-no-sympathy-for-paraguay-after-historic-world-cup-red-card</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Miguel Almirón sent off against Turkey for covering mouth  Socceroos face South Americans in crucial last Group D match  Socceroo Jackson Irvine has b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Egypt World Cup 2026: Fixtures, manager, squad depth and tactical analysis</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>7 hours ago</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/egypt-world-cup-2026-fixtures-players-analysis/</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Egypt are at the World Cup for the fourth time in their history. And they’ll be hoping to make it past the group stage for the first time.
 After a 1-</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Does it matter if Scotland lose and still make history?</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-06-21T21:39:43</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>How sweltering Scotland can handle World Cup heat</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-06-17T11:16:20</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Belgium World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>squawka</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>12 hours ago</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://www.squawka.com/en/news/world-cup/belgium-world-cup-2026-fixtures-squad-analysis-june-21/</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Belgium are back at the World Cup and desperate to give a much-improved account of themselves on the biggest stage. The Red Devils have got off to a s</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Does it matter if Scotland lose and still make history?</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-21T21:39:43</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>How sweltering Scotland can handle World Cup heat</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-17T11:16:20</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Belgium World Cup 2026: Fixtures, manager, squad depth &amp; tactical analysis</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>squawka</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>12 hours ago</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.squawka.com/en/news/world-cup/belgium-world-cup-2026-fixtures-squad-analysis-june-21/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Belgium are back at the World Cup and desperate to give a much-improved account of themselves on the biggest stage. The Red Devils have got off to a s</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Argentina vs Austria: predictions, best bets, stats &amp; odds</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>1 hour ago</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/argentina-vs-austria-predictions-betting-tips-22-06-26/</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t xml:space="preserve">No previous meetings between these teams.
 No price boosts for this event.
@@ -5443,31 +5804,55 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>World Cup 2026 Group F: Latest table, fixtures and results</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>1 day ago</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-group-f-latest-table-fixtures-and-results/</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t xml:space="preserve">Group F at World Cup 2026 looks to be one that has the potential for the biggest shock.
 The draw placed Netherlands into Group F alongside Japan and </t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cristian Romero Injury: Set for testing, hopeful of minor injury</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>rotowire</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.rotowire.com/soccer/headlines/cristian-romero-injury-set-for-testing-hopeful-of-minor-injury-520551</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Written by RotoWire Staff
+Romero (knee) is set for testing in the coming days, but is not expected to be anything significant, according to manager L</t>
         </is>
       </c>
     </row>

--- a/data/worldcup_0625_0623update.xlsx
+++ b/data/worldcup_0625_0623update.xlsx
@@ -1853,7 +1853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1891,7 +1891,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lawrence Shankland: Scotland not looking beyond crucial World Cup clash with Brazil</t>
+          <t>Scotland fans take over Miami Marlins game ahead of Brazil clash</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1901,24 +1901,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-22T20:10:53</t>
+          <t>2026-06-23T01:58:24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49146151/lawrence-shankland-scotland-focus-crucial-world-cup-clash-brazil</t>
+          <t>https://www.espn.com/video/clip/_/id/49149053/scotland-fans-take-miami-marlins-game-ahead-brazil-clash</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lawrence Shankland insists Scotland will ignore multiple permutations around possible qualification to go for the World Cup win against Brazil on Wedn</t>
+          <t>Scotland fans take over Miami Marlins game ahead of Brazil clash</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Neymar completes first World Cup training session before Brazil vs. Scotland</t>
+          <t>Lawrence Shankland: Scotland not looking beyond crucial World Cup clash with Brazil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1928,24 +1928,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-22T08:40:32</t>
+          <t>2026-06-22T20:10:53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49142107/neymar-completes-first-world-cup-training-session-brazil-vs-scotland</t>
+          <t>https://www.espn.com/soccer/story/_/id/49146151/lawrence-shankland-scotland-focus-crucial-world-cup-clash-brazil</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neymar completed his first full training session with Brazil on Sunday.</t>
+          <t>Lawrence Shankland insists Scotland will ignore multiple permutations around possible qualification to go for the World Cup win against Brazil on Wedn</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lucas Paqueta: Brazil have 'great respect' for Scotland</t>
+          <t>Neymar completes first World Cup training session before Brazil vs. Scotland</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1955,47 +1955,51 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-21T23:39:02</t>
+          <t>2026-06-22T08:40:32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/49138795/lucas-paqueta-brazil-scotland-fifa-world-cup-2026</t>
+          <t>https://www.espn.com/soccer/story/_/id/49142107/neymar-completes-first-world-cup-training-session-brazil-vs-scotland</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Brazil playmaker Lucas Paquetá says he has "great respect" for Scotland ahead of the decisive clash between the teams in Miami on Wednesday.</t>
+          <t>Neymar completed his first full training session with Brazil on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>官方：墨西哥裁判拉莫斯将执法世界杯苏格兰vs巴西</t>
+          <t>Lucas Paqueta: Brazil have 'great respect' for Scotland</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-21 20:39</t>
+          <t>2026-06-21T23:39:02</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955264.html</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>https://www.espn.com/soccer/story/_/id/49138795/lucas-paqueta-brazil-scotland-fifa-world-cup-2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Brazil playmaker Lucas Paquetá says he has "great respect" for Scotland ahead of the decisive clash between the teams in Miami on Wednesday.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>苏格兰主帅：对摩洛哥我们踢得有点慢热；末轮要死磕巴西</t>
+          <t>官方：墨西哥裁判拉莫斯将执法世界杯苏格兰vs巴西</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2005,12 +2009,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-21 00:26</t>
+          <t>2026-06-21 20:39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953238.html</t>
+          <t>https://www.dongqiudi.com/articles/5955264.html</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -2018,34 +2022,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
+          <t>苏格兰主帅：对摩洛哥我们踢得有点慢热；末轮要死磕巴西</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 13</t>
+          <t>2026-06-21 00:26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953238.html</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
+          <t>Guns for hire and gegenpress eggheads bring World Cup subplots aplenty</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2055,24 +2055,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 09</t>
+          <t>Sun, 21 Jun 2026 13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/football-daily-geopolitics-world-cup-maverick-managerial-matchups</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
+          <t>The awesome thing about a World Cup is that – unlike the Premier League where almost every elite-grade head coach comes from the same scenic Spanish t</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
+          <t>The French aristocrat and the all-American idiot: Henry v Lalas is the World Cup’s most compelling battle</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2082,24 +2082,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sun, 21 Jun 2026 04</t>
+          <t>Sun, 21 Jun 2026 09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/thierry-henry-alexi-lalas-fox-world-cup</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
+          <t xml:space="preserve">Fox’s broadcast at the tournament has become a story of two contrasting styles. And there is one clear winner  W e all know someone like Alexi Lalas. </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
+          <t>The 2026 World Cup team of the tournament so far (without the superstars)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2109,24 +2109,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sun Jun 21 2026 15:</t>
+          <t>Sun, 21 Jun 2026 04</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
+          <t>https://www.theguardian.com/football/2026/jun/21/the-2026-world-cup-team-of-the-tournament-so-far-without-the-superstars</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
+          <t>We pick an XI of players who have impressed during the initial rounds of games in Canada, the US and Mexico  A star was born, at 40, when a player who</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saibari strikes after 70 seconds as Morocco puncture Scotland’s World Cup party</t>
+          <t>Spain v Saudi Arabia: World Cup 2026 – live</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2136,24 +2136,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sat, 20 Jun 2026 00</t>
+          <t>Sun Jun 21 2026 15:</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/20/scotland-morocco-world-cup-match-report</t>
+          <t>https://www.theguardian.com/football/live/2026/jun/21/spain-v-saudi-arabia-world-cup-2026-live</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scotland would have taken this outcome after 70 seconds. Ismael Saibiri had fired this highly rated Morocco team ahead. Men in kilts gulped under the </t>
+          <t>⚽️ Kick-off: 12pm local time/5pm BST/2am (Mon) AEST ⚽️ Player guide | Bracketology | Golden Boot | Email John  Alex Reid has penned today’s weekend sp</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
+          <t>Saibari strikes after 70 seconds as Morocco puncture Scotland’s World Cup party</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2163,123 +2163,177 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fri, 19 Jun 2026 10</t>
+          <t>Sat, 20 Jun 2026 00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
+          <t>https://www.theguardian.com/football/2026/jun/20/scotland-morocco-world-cup-match-report</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
+          <t xml:space="preserve">Scotland would have taken this outcome after 70 seconds. Ismael Saibiri had fired this highly rated Morocco team ahead. Men in kilts gulped under the </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>How Ferguson became Scotland's most influential World Cup player</t>
+          <t>ITV wins World Cup ratings battle with BBC in tournament’s first week</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-22T17:39:02</t>
+          <t>Fri, 19 Jun 2026 10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c20y1zj927jo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.theguardian.com/football/2026/jun/19/itv-wins-world-cup-ratings-battle-bbc-first-week-england-croatia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lewis Ferguson earned his 26th Scotland cap in the 1-0 defeat to Morocco  Eight years ago, Lewis Ferguson had just departed Hamilton Academical.  A mu</t>
+          <t>England v Croatia attracted year’s highest UK TV figures  BBC opted for more first-pick games in knockout stages  ITV is winning the UK television rat</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Name the seven Scotland survivors from Clarke's first squad</t>
+          <t>Scotland's Tartan Army brings World Cup spirit to a Marlins game</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-22T07:46:18</t>
+          <t>2026-06-23T01:53:30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c05yze49v71o?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.espn.com/mlb/story/_/id/49148750/miami-marlins-scotland-tartan-army-2026-fifa-world-cup</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Seven years have passed since Steve Clarke named his first Scotland squad for Euro 2020 qualifiers against Cyprus and Belgium.  Seven players from tha</t>
+          <t>After celebrating with the Red Sox, members of Scotland's famed Tartan Army marched into loanDepot park and adopted the Marlins for a night.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Scotland's 2026 World Cup squad: All 26 players picked by Steve Clarke and why</t>
+          <t>How Ferguson became Scotland's most influential World Cup player</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>espn_pw</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-22T06:34:52</t>
+          <t>2026-06-22T17:39:02</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.espn.com/soccer/story/_/id/48769157/meet-scotland-2026-world-cup-squad-all-26-players-picked-steve-clarke-why</t>
+          <t>https://www.bbc.com/sport/football/articles/c20y1zj927jo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Scotland manager Steve Clarke has named the 26 players he believes can make an impression at the 2026 World Cup in the United States, Canada and Mexic</t>
+          <t>Lewis Ferguson earned his 26th Scotland cap in the 1-0 defeat to Morocco  Eight years ago, Lewis Ferguson had just departed Hamilton Academical.  A mu</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Name the seven Scotland survivors from Clarke's first squad</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-22T07:46:18</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/c05yze49v71o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Seven years have passed since Steve Clarke named his first Scotland squad for Euro 2020 qualifiers against Cyprus and Belgium.  Seven players from tha</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Scotland's 2026 World Cup squad: All 26 players picked by Steve Clarke and why</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>espn_pw</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-22T06:34:52</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.espn.com/soccer/story/_/id/48769157/meet-scotland-2026-world-cup-squad-all-26-players-picked-steve-clarke-why</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Scotland manager Steve Clarke has named the 26 players he believes can make an impression at the 2026 World Cup in the United States, Canada and Mexic</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>4-0突尼斯，日本终结连续5届世界杯小组赛第二轮不胜魔咒</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>dongqiudi</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>2026-06-22 07:41</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>https://www.dongqiudi.com/article/5956343</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>世界杯小组赛第二轮，日本对阵突尼斯，最终日本国家队4-0大胜突尼斯。
 据统计，日本本轮大胜后终结了连续5届世界杯小组赛第二轮不胜魔咒，自2006年世界杯以来，日本队在世界杯小组赛第二轮未尝胜绩，本届世界杯终于打破魔咒。
@@ -2289,64 +2343,10 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Does it matter if Scotland lose and still make history?</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>bbc_sport</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-06-21T21:39:43</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Scotland World Cup injury concerns as Aaron Hickey, Scott McKenna, Lewis Ferguson miss training</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>espn_pw</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-06-21T21:00:44</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://www.espn.com/soccer/story/_/id/49135824/scotland-injury-concerns-aaron-hickey-scott-mckenna-lewis-ferguson-miss-training-world-cup</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Aaron Hickey, Scott McKenna and Lewis Ferguson missed group training ahead of Scotland's final World Cup Group C fixture against Brazil on Wednesday.</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>What have we learned from Scotland's World Cup so far?</t>
+          <t>Does it matter if Scotland lose and still make history?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2356,70 +2356,78 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-21T13:14:21</t>
+          <t>2026-06-21T21:39:43</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/c79yq0yx10ro?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.bbc.com/sport/football/articles/ckg0exlle8yo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Steve Clarke is bidding to become the first manager to steer Scotland beyond the group stage of a major tournament  After two World Cup outings, Scotl</t>
+          <t>Steve Clarke and his squad are preparing for a potentially historic game  In a World Cup where the boffins with their big brainy heads and their super</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>官方：巴西裁判阿巴蒂将执法世界杯瑞士vs加拿大</t>
+          <t>Scotland World Cup injury concerns as Aaron Hickey, Scott McKenna, Lewis Ferguson miss training</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>espn_pw</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-21 20:48</t>
+          <t>2026-06-21T21:00:44</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955280.html</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>https://www.espn.com/soccer/story/_/id/49135824/scotland-injury-concerns-aaron-hickey-scott-mckenna-lewis-ferguson-miss-training-world-cup</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aaron Hickey, Scott McKenna and Lewis Ferguson missed group training ahead of Scotland's final World Cup Group C fixture against Brazil on Wednesday.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>荷兰5球大胜瑞典，世界杯连续不败场次超越贝利时代巴西</t>
+          <t>What have we learned from Scotland's World Cup so far?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>bbc_sport</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-21 20:21</t>
+          <t>2026-06-21T13:14:21</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955233.html</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>https://www.bbc.com/sport/football/articles/c79yq0yx10ro?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Steve Clarke is bidding to become the first manager to steer Scotland beyond the group stage of a major tournament  After two World Cup outings, Scotl</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>巴媒：内马尔恢复有球训练，力争对苏格兰完成世界杯首秀</t>
+          <t>官方：巴西裁判阿巴蒂将执法世界杯瑞士vs加拿大</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2429,12 +2437,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-21 07:27</t>
+          <t>2026-06-21 20:48</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5953848.html</t>
+          <t>https://www.dongqiudi.com/articles/5955280.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -2442,218 +2450,218 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Neymar set for Scotland return as Raphinha faces World Cup setback</t>
+          <t>荷兰5球大胜瑞典，世界杯连续不败场次超越贝利时代巴西</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-20T16:28:34</t>
+          <t>2026-06-21 20:21</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/neymar-set-for-scotland-return-as-raphinha-faces-world-cup-setback</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carlo Ancelotti has confirmed he expects Neymar to be available for Brazil’s final Group C match against Scotland at the World Cup. However, Raphinha </t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5955233.html</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>How does qualification for the World Cup knockout stage work?</t>
+          <t>巴媒：内马尔恢复有球训练，力争对苏格兰完成世界杯首秀</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-20T16:24:00</t>
+          <t>2026-06-21 07:27</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5953848.html</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Neymar set for Scotland return as Raphinha faces World Cup setback</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sofascore</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:28:34</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.sofascore.com/news/neymar-set-for-scotland-return-as-raphinha-faces-world-cup-setback</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carlo Ancelotti has confirmed he expects Neymar to be available for Brazil’s final Group C match against Scotland at the World Cup. However, Raphinha </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>How does qualification for the World Cup knockout stage work?</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-20T16:24:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cp8l6zj8441o?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>England are aiming to win Group L - but their potential path to the final is tricky  As the planet's elite footballers put every effort into qualifyin</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Cunha riding wave of success after brilliant Brazil brace</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>2026-06-20T05:40:00</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/matheus-cunha-brazil-reaction-haiti</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Four years after missing out on Qatar 2022, surfing fan Matheus Cunha scored his first FIFA World Cup goals as Brazil beat Haiti 3-0.
 After waiting f</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>The best photos from Matchday 9</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>2026-06-20T05:00:00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/best-photos-matchday-9</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Enjoy an array of the best photos from the most recent round of fixtures at the FIFA World Cup 2026.
 Two USA fans dressed as bald eagles pose ahead o</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Six players climbing the FIFA Power Rankings</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2026-06-20T04:00:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/six-players-climbing-fifa-power-rankings</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">From Jonathan David and Matheus Cunha to Lucas Paqueta and Chris Richards, see which players have risen swiftly up the FIFA Power Rankings.
 Jonathan </t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Vinicius Jr. hits the ground running with Brazil</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>fifa</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-06-20T04:00:00</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://www.fifa.com/en/articles/vinicius-jr-brazil-great-start</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>The No. 7 has been involved in all of Brazil's goals so far in the World Cup and has surpassed stars like Romario and Ronaldinho in efficiency per gam</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>巴西队美加墨周期纪实39：世界杯小组赛3-0轻取海地</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-06-20 17:59</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5951203.html</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-    </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>老熟人来了，瓜迪奥拉现身世界杯球场看台观战苏格兰vs摩洛哥</t>
+          <t>Vinicius Jr. hits the ground running with Brazil</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>fifa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-20 14:52</t>
+          <t>2026-06-20T04:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951666.html</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>https://www.fifa.com/en/articles/vinicius-jr-brazil-great-start</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>The No. 7 has been involved in all of Brazil's goals so far in the World Cup and has surpassed stars like Romario and Ronaldinho in efficiency per gam</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>巴西3-0海地登顶C组，卡塞米罗：世界杯无易战</t>
+          <t>巴西队美加墨周期纪实39：世界杯小组赛3-0轻取海地</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2663,12 +2671,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-20 12:56</t>
+          <t>2026-06-20 17:59</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951477.html</t>
+          <t>https://www.dongqiudi.com/articles/5951203.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -2676,7 +2684,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>世界杯积分新规，巴西3:0海地，海地成为第一支出...</t>
+          <t>老熟人来了，瓜迪奥拉现身世界杯球场看台观战苏格兰vs摩洛哥</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2686,12 +2694,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-06-20 10:46</t>
+          <t>2026-06-20 14:52</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951242.html</t>
+          <t>https://www.dongqiudi.com/articles/5951666.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -2699,7 +2707,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8胜1平8次零封，巴西在世界杯面对中北美球队战绩碾压</t>
+          <t>巴西3-0海地登顶C组，卡塞米罗：世界杯无易战</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2709,12 +2717,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06-20 07:12</t>
+          <t>2026-06-20 12:56</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5950880.html</t>
+          <t>https://www.dongqiudi.com/articles/5951477.html</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2722,88 +2730,80 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazil vs Haiti Prediction: World Cup 2026 Match Preview</t>
+          <t>世界杯积分新规，巴西3:0海地，海地成为第一支出...</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-06-19T21:55:38</t>
+          <t>2026-06-20 10:46</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/brazil-vs-haiti-prediction-world-cup-2026-match-preview/</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Brazil are out to secure a first win of their World Cup 2026 campaign when they face off against Haiti in Philadelphia. Look ahead to the Group C cont</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5951242.html</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brazil vs Haiti preview: Group C stakes, key trends and a few numbers you’ll want to know</t>
+          <t>8胜1平8次零封，巴西在世界杯面对中北美球队战绩碾压</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sofascore</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-06-19T13:00:00</t>
+          <t>2026-06-20 07:12</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/brazil-vs-haiti-preview-group-c-stakes-key-trends-and-a-few-numbers-youll-want-to-know</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Brazil face Haiti in World Cup 2026 Group C. Form trends, key stats, decimal odds, team news and Sofascore Rating standouts to know before kickoff.</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5950880.html</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>World Cup 2026: Routes to the final</t>
+          <t>Brazil vs Haiti Prediction: World Cup 2026 Match Preview</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>fifa</t>
+          <t>theanalyst_api</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-06-19T12:00:00</t>
+          <t>2026-06-19T21:55:38</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
+          <t>https://theanalyst.com/articles/brazil-vs-haiti-prediction-world-cup-2026-match-preview/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
+          <t>Brazil are out to secure a first win of their World Cup 2026 campaign when they face off against Haiti in Philadelphia. Look ahead to the Group C cont</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Scotland vs Morocco preview: World Cup Group C</t>
+          <t>Brazil vs Haiti preview: Group C stakes, key trends and a few numbers you’ll want to know</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2813,163 +2813,171 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-06-19T12:00:00</t>
+          <t>2026-06-19T13:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.sofascore.com/news/scotland-vs-morocco-preview-world-cup-group-c</t>
+          <t>https://www.sofascore.com/news/brazil-vs-haiti-preview-group-c-stakes-key-trends-and-a-few-numbers-youll-want-to-know</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Scotland face Morocco at Gillette Stadium in World Cup 2026 Group C. Form, H2H, odds, lineups and the key Sofascore Rating standouts set the stage.</t>
+          <t>Brazil face Haiti in World Cup 2026 Group C. Form trends, key stats, decimal odds, team news and Sofascore Rating standouts to know before kickoff.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Scotland vs Morocco Prediction: World Cup 2026 Match Preview</t>
+          <t>World Cup 2026: Routes to the final</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>theanalyst_api</t>
+          <t>fifa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-06-19T08:13:48</t>
+          <t>2026-06-19T12:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://theanalyst.com/articles/scotland-vs-morocco-prediction-world-cup-2026-match-preview/</t>
+          <t>https://www.fifa.com/en/articles/group-stage-permutations-qualify</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>After a pair of exciting curtain-raisers, the top two sides in Group C will now face off in Boston. Look ahead to Friday’s FIFA World Cup clash with o</t>
+          <t>Find out what every team needs to qualify for the Round of 32 as group winners or runners-up, with information on Groups A-L, plus the tournament brac</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>How sweltering Scotland can handle World Cup heat</t>
+          <t>Scotland vs Morocco preview: World Cup Group C</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bbc_sport</t>
+          <t>sofascore</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-06-17T11:16:20</t>
+          <t>2026-06-19T12:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
+          <t>https://www.sofascore.com/news/scotland-vs-morocco-preview-world-cup-group-c</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
+          <t>Scotland face Morocco at Gillette Stadium in World Cup 2026 Group C. Form, H2H, odds, lineups and the key Sofascore Rating standouts set the stage.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Scotland vs Morocco Prediction: World Cup 2026 Match Preview</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>theanalyst_api</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-06-19T08:13:48</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/scotland-vs-morocco-prediction-world-cup-2026-match-preview/</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>After a pair of exciting curtain-raisers, the top two sides in Group C will now face off in Boston. Look ahead to Friday’s FIFA World Cup clash with o</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>How sweltering Scotland can handle World Cup heat</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>bbc_sport</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-06-17T11:16:20</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.bbc.com/sport/football/articles/cx26geg0elgo?at_medium=RSS&amp;at_campaign=rss</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Scotland will face sweltering conditions in their final Group C match  Hydration breaks, ice jackets, cooling towels and isotonic drinks have been a f</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Neymar Injury: Trains without limitations</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>rotowire</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>https://www.rotowire.com/soccer/headlines/neymar-injury-trains-without-limitations-520556</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Written by RotoWire Staff
 Neymar (calf) trained without limitations Monday as his availability for Wednesday's match against Scotland is further rein</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>联手梅西！罗马诺：卡塞米罗还收到欧洲沙特报价 他与迈阿密签3年</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>zhibo8</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2026-06-22 15:35:00</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e37c69ad1native.htm</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>帕奎塔：和维尼修斯一起踢球很快乐；我们都为内马尔回归高兴</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-06-22 03:33</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5955960.html</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-    </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ESPN：内马尔将入选对阵苏格兰比赛名单，但不会扮演重要角色</t>
+          <t>联手梅西！罗马诺：卡塞米罗还收到欧洲沙特报价 他与迈阿密签3年</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>dongqiudi_team</t>
+          <t>zhibo8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-06-22 00:48</t>
+          <t>2026-06-22 15:35:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955754.html</t>
+          <t>https://m.zhibo8.com/news/web/zuqiu/2026-06-22/6a38e37c69ad1native.htm</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2977,7 +2985,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TA：巴西全民紧盯内马尔和恩德里克，真正的救星却是库尼亚</t>
+          <t>帕奎塔：和维尼修斯一起踢球很快乐；我们都为内马尔回归高兴</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2987,12 +2995,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-06-22 00:02</t>
+          <t>2026-06-22 03:33</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5955612.html</t>
+          <t>https://www.dongqiudi.com/articles/5955960.html</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -3000,7 +3008,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>利物浦球员国家队战报：阿利松80场里程碑多次扑救+零封</t>
+          <t>ESPN：内马尔将入选对阵苏格兰比赛名单，但不会扮演重要角色</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3010,12 +3018,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-06-20 11:15</t>
+          <t>2026-06-22 00:48</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.dongqiudi.com/articles/5951315.html</t>
+          <t>https://www.dongqiudi.com/articles/5955754.html</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -3023,18 +3031,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>图片报：检察机关调查博彩运营商Blaze，内马尔曾与之合作</t>
+          <t>TA：巴西全民紧盯内马尔和恩德里克，真正的救星却是库尼亚</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>dongqiudi</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-06-22 00:02</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959123&amp;from=tab_253</t>
+          <t>https://www.dongqiudi.com/articles/5955612.html</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3042,181 +3054,223 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Maybe this World Cup will bring the best out of the US, not the worst</t>
+          <t>利物浦球员国家队战报：阿利松80场里程碑多次扑救+零封</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>dongqiudi_team</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mon, 22 Jun 2026 04</t>
+          <t>2026-06-20 11:15</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-2026-us-united-states-usa-co-host-nation</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Tournament could hold up a useful hand mirror to the isolationism and divisiveness of Trump’s joint-host nation  O ne of the best parts of following f</t>
-        </is>
-      </c>
+          <t>https://www.dongqiudi.com/articles/5951315.html</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>图片报：检察机关调查博彩运营商Blaze，内马尔曾与之合作</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>dongqiudi</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://n.dongqiudi.com/webapp/news.html?articleId=5959123&amp;from=tab_253</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Maybe this World Cup will bring the best out of the US, not the worst</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 04</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.theguardian.com/football/2026/jun/22/world-cup-2026-us-united-states-usa-co-host-nation</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Tournament could hold up a useful hand mirror to the isolationism and divisiveness of Trump’s joint-host nation  O ne of the best parts of following f</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>World Cup 2026 fixtures and results: Every fixture and kick-off time for the biggest World Cup ever</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>6 days ago</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/world-cup-2026-fixtures-results/</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t xml:space="preserve">The 2026 World Cup is now well underway. Find the latest World Cup results and upcoming fixtures here.
 Get the latest World Cup Group A betting odds </t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>What did we learn after the second round of Group C</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>sofascore</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>2026-06-21T15:21:15</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>https://www.sofascore.com/news/what-did-we-learn-after-the-second-round-of-group-c</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Aimar: Messi has made us expect the unexpected</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>fifa</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>2026-06-21T03:30:00</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>https://www.fifa.com/en/articles/pablo-aimar-messi</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Lionel Scaloni’s assistant on the Argentina bench discusses his relationship with the captain and La Albiceleste’s recent success.
 At the age of 12 o</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Scotland 0-1 Morocco Stats: Early Saibari Stunner Settles Group C Clash</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>theanalyst</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-06-20T01:12:39</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://theanalyst.com/articles/scotland-vs-morocco-stats-fifa-world-cup-2026-live</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Follow the action live as Scotland look to make it two wins from two at the 2026 FIFA World Cup against African giants Morocco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C组积分榜：巴西积4分领先摩洛哥2粒净胜球，海地提前出局</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>dongqiudi_team</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-06-20 10:44</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://www.dongqiudi.com/articles/5951239.html</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-    </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Scotland 0-1 Morocco Stats: Early Saibari Stunner Settles Group C Clash</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>theanalyst</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-06-20T01:12:39</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://theanalyst.com/articles/scotland-vs-morocco-stats-fifa-world-cup-2026-live</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Follow the action live as Scotland look to make it two wins from two at the 2026 FIFA World Cup against African giants Morocco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>C组积分榜：巴西积4分领先摩洛哥2粒净胜球，海地提前出局</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>dongqiudi_team</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-06-20 10:44</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.dongqiudi.com/articles/5951239.html</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>Spain World Cup 2026: Fixtures, results, manager, squad depth and tactical analysis</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>squawka</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>15 hours ago</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>https://www.squawka.com/en/news/world-cup/spain-world-cup-2026-fixtures-results-squad-analysis/</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Spain ’s 2026 World Cup campaign took a sharp turn in North America as they followed up a frustrating opening draw with Cape Verde by producing a comm</t>
         </is>
